--- a/pipeline/outputs/matrix_finetuned_epoch3_s3_vs_finetuned_epoch3_s3_net.xlsx
+++ b/pipeline/outputs/matrix_finetuned_epoch3_s3_vs_finetuned_epoch3_s3_net.xlsx
@@ -947,10 +947,10 @@
         <v>99.75</v>
       </c>
       <c r="L8" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M8" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N8" t="n">
         <v>98.59999999999999</v>
@@ -1011,10 +1011,10 @@
         <v>98.98999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M9" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N9" t="n">
         <v>97.40000000000001</v>
@@ -1075,10 +1075,10 @@
         <v>99.51000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M10" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N10" t="n">
         <v>97.3</v>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="11">
@@ -1636,20 +1636,20 @@
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>75.73</v>
+        <v>77.67</v>
       </c>
       <c r="L19" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M19" t="n">
         <v>103</v>
       </c>
       <c r="N19" t="n">
-        <v>66.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="20">
@@ -1756,20 +1756,20 @@
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L21" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
       </c>
       <c r="N21" t="n">
-        <v>43.3</v>
+        <v>44.3</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2468,20 +2468,20 @@
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
-        <v>82.67</v>
+        <v>85.33</v>
       </c>
       <c r="L33" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M33" t="n">
         <v>75</v>
       </c>
       <c r="N33" t="n">
-        <v>72.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>4</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="34">
@@ -3264,20 +3264,20 @@
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
-        <v>86.25</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="L47" t="n">
         <v>69</v>
       </c>
       <c r="M47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N47" t="n">
-        <v>77</v>
+        <v>74.7</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>-0.42</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="48">
@@ -3320,20 +3320,20 @@
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="n">
-        <v>82.45999999999999</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="M48" t="n">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="N48" t="n">
         <v>80.2</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="49">
@@ -3376,20 +3376,20 @@
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="n">
-        <v>91.14</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="M49" t="n">
         <v>1083</v>
       </c>
       <c r="N49" t="n">
-        <v>89.3</v>
+        <v>89.5</v>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="50">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>85</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="47">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>76.8</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>82.90000000000001</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>77.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>82.7</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="74">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="77">
